--- a/Templates/bulkImport/config/construct_RFIT_config_sabah.xlsx
+++ b/Templates/bulkImport/config/construct_RFIT_config_sabah.xlsx
@@ -4,30 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9024"/>
   </bookViews>
   <sheets>
     <sheet name="construct_RFI_config_sabah" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
   <si>
     <t>*</t>
   </si>
@@ -41,18 +28,12 @@
     <t>c_date_request</t>
   </si>
   <si>
+    <t>c_subject</t>
+  </si>
+  <si>
     <t>c_work_discipline</t>
   </si>
   <si>
-    <t>c_utility_provider</t>
-  </si>
-  <si>
-    <t>c_utility_provider_other</t>
-  </si>
-  <si>
-    <t>c_subject</t>
-  </si>
-  <si>
     <t>c_location</t>
   </si>
   <si>
@@ -62,16 +43,25 @@
     <t>c_file</t>
   </si>
   <si>
-    <t>c_rfit_cost_implication</t>
-  </si>
-  <si>
-    <t>c_rfit_time_implication</t>
-  </si>
-  <si>
-    <t>c_requested_by</t>
-  </si>
-  <si>
-    <t>c_remarks</t>
+    <t>c_issued_by</t>
+  </si>
+  <si>
+    <t>c_date_issued</t>
+  </si>
+  <si>
+    <t>c_response_desc</t>
+  </si>
+  <si>
+    <t>c_re_applicable</t>
+  </si>
+  <si>
+    <t>c_reviewed_by</t>
+  </si>
+  <si>
+    <t>c_acknowledged_date</t>
+  </si>
+  <si>
+    <t>c_acknowledged_by</t>
   </si>
   <si>
     <t>c_actioner</t>
@@ -80,171 +70,21 @@
     <t>c_action</t>
   </si>
   <si>
-    <t>c_action_date</t>
-  </si>
-  <si>
     <t>c_status</t>
   </si>
   <si>
-    <t>c_issued_by</t>
-  </si>
-  <si>
-    <t>c_date_issued</t>
-  </si>
-  <si>
-    <t>c_issue_designation</t>
-  </si>
-  <si>
-    <t>c_issuer_remark</t>
-  </si>
-  <si>
-    <t>c_rfi_acknowledge</t>
-  </si>
-  <si>
-    <t>c_acknowledged_by</t>
-  </si>
-  <si>
-    <t>c_acknowledge_position</t>
-  </si>
-  <si>
-    <t>c_acknowledge_company</t>
-  </si>
-  <si>
-    <t>c_acknowledged_time</t>
-  </si>
-  <si>
-    <t>c_acknowledged_date</t>
-  </si>
-  <si>
-    <t>c_response_desc</t>
-  </si>
-  <si>
-    <t>c_re_applicable</t>
-  </si>
-  <si>
-    <t>c_re_applicable_remarks</t>
-  </si>
-  <si>
-    <t>c_response_file</t>
-  </si>
-  <si>
-    <t>c_cost_implication</t>
-  </si>
-  <si>
-    <t>c_time_extension</t>
-  </si>
-  <si>
-    <t>c_reviewed_by</t>
-  </si>
-  <si>
-    <t>c_respond_designation</t>
-  </si>
-  <si>
-    <t>c_reviewer_organization</t>
-  </si>
-  <si>
-    <t>c_reviewed_date</t>
-  </si>
-  <si>
-    <t>c_rfi_acknowledge2</t>
-  </si>
-  <si>
-    <t>c_acknowledged_by2</t>
-  </si>
-  <si>
-    <t>c_acknowledge_position2</t>
-  </si>
-  <si>
-    <t>c_acknowledged_time2</t>
-  </si>
-  <si>
-    <t>c_acknowledged_date2</t>
-  </si>
-  <si>
-    <t>c_response_desc2</t>
-  </si>
-  <si>
-    <t>c_recommendation</t>
-  </si>
-  <si>
-    <t>c_response_remarks2</t>
-  </si>
-  <si>
-    <t>c_response_file2</t>
-  </si>
-  <si>
-    <t>c_reviewed_by2</t>
-  </si>
-  <si>
-    <t>c_respond_designation2</t>
-  </si>
-  <si>
-    <t>c_reviewer_organization2</t>
-  </si>
-  <si>
-    <t>c_reviewed_date2</t>
-  </si>
-  <si>
-    <t>c_response_desc3</t>
-  </si>
-  <si>
-    <t>c_response_file3</t>
-  </si>
-  <si>
-    <t>c_reviewed_by3</t>
-  </si>
-  <si>
-    <t>c_respond_designation3</t>
-  </si>
-  <si>
-    <t>c_reviewer_organization3</t>
-  </si>
-  <si>
-    <t>c_reviewed_date3</t>
-  </si>
-  <si>
-    <t>c_compile_dcr</t>
-  </si>
-  <si>
-    <t>c_compile_remarks</t>
-  </si>
-  <si>
-    <t>c_compile_file</t>
-  </si>
-  <si>
-    <t>c_compile_reviewed_by</t>
-  </si>
-  <si>
-    <t>c_compile_reviewer_organization</t>
-  </si>
-  <si>
-    <t>c_compile_reviewed_date</t>
-  </si>
-  <si>
-    <t>c_closed_remark</t>
-  </si>
-  <si>
-    <t>c_close_attachment</t>
-  </si>
-  <si>
     <t>RFIT No.</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
+    <t>RFIT Subject Title</t>
+  </si>
+  <si>
     <t>Work Discipline</t>
   </si>
   <si>
-    <t>Utility Provider</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Utility Provider Other</t>
-  </si>
-  <si>
-    <t>RFIT Subject Title</t>
-  </si>
-  <si>
     <t>Location/Chainage</t>
   </si>
   <si>
@@ -254,16 +94,25 @@
     <t>Attachment(s)</t>
   </si>
   <si>
-    <t>Cost Implication?</t>
-  </si>
-  <si>
-    <t>Time Implication?</t>
-  </si>
-  <si>
-    <t>Requested By</t>
-  </si>
-  <si>
-    <t>Remarks</t>
+    <t>Issued By</t>
+  </si>
+  <si>
+    <t>Issued Date</t>
+  </si>
+  <si>
+    <t>Response (RE)</t>
+  </si>
+  <si>
+    <t>Applicable for Consultant RE to Review?</t>
+  </si>
+  <si>
+    <t>Reviewed &amp; Approved By</t>
+  </si>
+  <si>
+    <t>Acknowledge Date</t>
+  </si>
+  <si>
+    <t>Acknowledge By</t>
   </si>
   <si>
     <t>Actioner</t>
@@ -272,160 +121,13 @@
     <t>Action</t>
   </si>
   <si>
-    <t>Action Date</t>
-  </si>
-  <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>Issued By</t>
-  </si>
-  <si>
-    <t>Issued Date</t>
-  </si>
-  <si>
-    <t>Issue Designation</t>
-  </si>
-  <si>
-    <t>Issue Remark</t>
-  </si>
-  <si>
-    <t>Acknowledge?</t>
-  </si>
-  <si>
-    <t>Acknowledged Name</t>
-  </si>
-  <si>
-    <t>Acknowledged Position</t>
-  </si>
-  <si>
-    <t>Acknowledged Company</t>
-  </si>
-  <si>
-    <t>Acknowledge Time</t>
-  </si>
-  <si>
-    <t>Acknowledge Date</t>
-  </si>
-  <si>
-    <t>Response (RE)</t>
-  </si>
-  <si>
-    <t>Applicable for Consultant RE to Review?</t>
-  </si>
-  <si>
-    <t>Response Remarks</t>
-  </si>
-  <si>
-    <t>Response Attachment(s)</t>
-  </si>
-  <si>
-    <t>Time Extension?</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Approved By</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Approved Designation</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Approved Organization</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Approved Date</t>
-  </si>
-  <si>
-    <t>Acknowledge (PMC)</t>
-  </si>
-  <si>
-    <t>Acknowledge (PMC) By</t>
-  </si>
-  <si>
-    <t>Acknowledge (PMC) Position</t>
-  </si>
-  <si>
-    <t>Acknowledge (PMC) Time</t>
-  </si>
-  <si>
-    <t>Acknowledge (PMC) Date</t>
-  </si>
-  <si>
-    <t>Response (PMC)</t>
-  </si>
-  <si>
-    <t>Response (PMC) Recommendation</t>
-  </si>
-  <si>
-    <t>Response (PMC) Remarks</t>
-  </si>
-  <si>
-    <t>Response (PMC) attachment(s)</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Response (PMC) By</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Response (PMC) Designation</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Response (PMC) Organization</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Response (PMC) Date</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Response (SOR) Response</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Approved (SOR) Attachment(s)</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Response (SOR) By</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Response (SOR) Designation</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Response (SOR) Organization</t>
-  </si>
-  <si>
-    <t>Reviewed &amp; Response (SOR) Date</t>
-  </si>
-  <si>
-    <t>Design Change Request (DCR) ?</t>
-  </si>
-  <si>
-    <t>Design Change Request (DCR) Cost Implication?</t>
-  </si>
-  <si>
-    <t>Design Change Request (DCR) Time Extension?</t>
-  </si>
-  <si>
-    <t>Design Change Request (DCR) Remarks</t>
-  </si>
-  <si>
-    <t>Design Change Request (DCR) Attachment(s)</t>
-  </si>
-  <si>
-    <t>Compile &amp; Reviewed By</t>
-  </si>
-  <si>
-    <t>Compile &amp; Reviewed Organization</t>
-  </si>
-  <si>
-    <t>Compile &amp; Reviewed Date</t>
-  </si>
-  <si>
-    <t>Closed Remarks</t>
-  </si>
-  <si>
-    <t>Close Attachment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
@@ -1389,28 +1091,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BN5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="3" max="3" width="16.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="16.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="22.7777777777778" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" customWidth="1"/>
-    <col min="9" max="9" width="22.3333333333333" customWidth="1"/>
-    <col min="10" max="13" width="11.6666666666667" customWidth="1"/>
-    <col min="14" max="15" width="21.8888888888889" customWidth="1"/>
-    <col min="16" max="16" width="14.5555555555556" customWidth="1"/>
-    <col min="17" max="17" width="8.44444444444444" customWidth="1"/>
-    <col min="18" max="18" width="11.6666666666667" customWidth="1"/>
-    <col min="19" max="25" width="15" customWidth="1"/>
-    <col min="26" max="26" width="21.1111111111111" customWidth="1"/>
-    <col min="27" max="27" width="15" customWidth="1"/>
-    <col min="28" max="28" width="16.2222222222222" customWidth="1"/>
-    <col min="29" max="29" width="15" customWidth="1"/>
-    <col min="30" max="65" width="21.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="7" max="7" width="22.3333333333333" customWidth="1"/>
+    <col min="9" max="11" width="15" customWidth="1"/>
+    <col min="12" max="13" width="21.6666666666667" customWidth="1"/>
+    <col min="14" max="16" width="21.8888888888889" customWidth="1"/>
+    <col min="17" max="17" width="6.44444444444444" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1420,11 +1112,11 @@
       <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:66">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1476,155 +1168,8 @@
       <c r="Q2" t="s">
         <v>1</v>
       </c>
-      <c r="R2" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W2" t="s">
-        <v>1</v>
-      </c>
-      <c r="X2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>1</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:66">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1676,155 +1221,8 @@
       <c r="Q3">
         <v>16</v>
       </c>
-      <c r="R3">
-        <v>17</v>
-      </c>
-      <c r="S3">
-        <v>18</v>
-      </c>
-      <c r="T3">
-        <v>19</v>
-      </c>
-      <c r="U3">
-        <v>20</v>
-      </c>
-      <c r="V3">
-        <v>21</v>
-      </c>
-      <c r="W3">
-        <v>22</v>
-      </c>
-      <c r="X3">
-        <v>23</v>
-      </c>
-      <c r="Y3">
-        <v>24</v>
-      </c>
-      <c r="Z3">
-        <v>25</v>
-      </c>
-      <c r="AA3">
-        <v>26</v>
-      </c>
-      <c r="AB3">
-        <v>27</v>
-      </c>
-      <c r="AC3">
-        <v>28</v>
-      </c>
-      <c r="AD3">
-        <v>29</v>
-      </c>
-      <c r="AE3">
-        <v>30</v>
-      </c>
-      <c r="AF3">
-        <v>31</v>
-      </c>
-      <c r="AG3">
-        <v>32</v>
-      </c>
-      <c r="AH3">
-        <v>33</v>
-      </c>
-      <c r="AI3">
-        <v>34</v>
-      </c>
-      <c r="AJ3">
-        <v>35</v>
-      </c>
-      <c r="AK3">
-        <v>36</v>
-      </c>
-      <c r="AL3">
-        <v>37</v>
-      </c>
-      <c r="AM3">
-        <v>38</v>
-      </c>
-      <c r="AN3">
-        <v>39</v>
-      </c>
-      <c r="AO3">
-        <v>40</v>
-      </c>
-      <c r="AP3">
-        <v>41</v>
-      </c>
-      <c r="AQ3">
-        <v>42</v>
-      </c>
-      <c r="AR3">
-        <v>43</v>
-      </c>
-      <c r="AS3">
-        <v>44</v>
-      </c>
-      <c r="AT3">
-        <v>45</v>
-      </c>
-      <c r="AU3">
-        <v>46</v>
-      </c>
-      <c r="AV3">
-        <v>47</v>
-      </c>
-      <c r="AW3">
-        <v>48</v>
-      </c>
-      <c r="AX3">
-        <v>49</v>
-      </c>
-      <c r="AY3">
-        <v>50</v>
-      </c>
-      <c r="AZ3">
-        <v>51</v>
-      </c>
-      <c r="BA3">
-        <v>52</v>
-      </c>
-      <c r="BB3">
-        <v>53</v>
-      </c>
-      <c r="BC3">
-        <v>54</v>
-      </c>
-      <c r="BD3">
-        <v>55</v>
-      </c>
-      <c r="BE3">
-        <v>56</v>
-      </c>
-      <c r="BF3">
-        <v>57</v>
-      </c>
-      <c r="BG3">
-        <v>58</v>
-      </c>
-      <c r="BH3">
-        <v>59</v>
-      </c>
-      <c r="BI3">
-        <v>60</v>
-      </c>
-      <c r="BJ3">
-        <v>61</v>
-      </c>
-      <c r="BK3">
-        <v>62</v>
-      </c>
-      <c r="BL3">
-        <v>63</v>
-      </c>
-      <c r="BM3">
-        <v>64</v>
-      </c>
-      <c r="BN3">
-        <v>65</v>
-      </c>
     </row>
-    <row r="4" spans="1:66">
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1876,352 +1274,58 @@
       <c r="Q4" t="s">
         <v>18</v>
       </c>
-      <c r="R4" t="s">
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="S4" t="s">
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="T4" t="s">
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="U4" t="s">
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="V4" t="s">
+      <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="W4" t="s">
+      <c r="F5" t="s">
         <v>24</v>
       </c>
-      <c r="X4" t="s">
+      <c r="G5" t="s">
         <v>25</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="H5" t="s">
         <v>26</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="I5" t="s">
         <v>27</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="J5" t="s">
         <v>28</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="K5" t="s">
         <v>29</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="L5" t="s">
         <v>30</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="M5" t="s">
         <v>31</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="N5" t="s">
         <v>32</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="O5" t="s">
         <v>33</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="P5" t="s">
         <v>34</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="Q5" t="s">
         <v>35</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>53</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>54</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>55</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>56</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>57</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>58</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>33</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>34</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>59</v>
-      </c>
-      <c r="BI4" t="s">
-        <v>60</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>61</v>
-      </c>
-      <c r="BK4" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>63</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>64</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:66">
-      <c r="A5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J5" t="s">
-        <v>75</v>
-      </c>
-      <c r="K5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L5" t="s">
-        <v>77</v>
-      </c>
-      <c r="M5" t="s">
-        <v>78</v>
-      </c>
-      <c r="N5" t="s">
-        <v>79</v>
-      </c>
-      <c r="O5" t="s">
-        <v>80</v>
-      </c>
-      <c r="P5" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>82</v>
-      </c>
-      <c r="R5" t="s">
-        <v>83</v>
-      </c>
-      <c r="S5" t="s">
-        <v>84</v>
-      </c>
-      <c r="T5" t="s">
-        <v>85</v>
-      </c>
-      <c r="U5" t="s">
-        <v>86</v>
-      </c>
-      <c r="V5" t="s">
-        <v>87</v>
-      </c>
-      <c r="W5" t="s">
-        <v>88</v>
-      </c>
-      <c r="X5" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>99</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>101</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>103</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>104</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>105</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>106</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>107</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>109</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>110</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>111</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>112</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>113</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>114</v>
-      </c>
-      <c r="AY5" t="s">
-        <v>115</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>116</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>118</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>119</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>120</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>121</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>122</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>123</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>124</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>125</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>126</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>127</v>
-      </c>
-      <c r="BL5" t="s">
-        <v>128</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>129</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Templates/bulkImport/config/construct_RFIT_config_sabah.xlsx
+++ b/Templates/bulkImport/config/construct_RFIT_config_sabah.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9024"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="construct_RFI_config_sabah" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="131">
   <si>
     <t>*</t>
   </si>
@@ -28,12 +41,18 @@
     <t>c_date_request</t>
   </si>
   <si>
+    <t>c_work_discipline</t>
+  </si>
+  <si>
+    <t>c_utility_provider</t>
+  </si>
+  <si>
+    <t>c_utility_provider_other</t>
+  </si>
+  <si>
     <t>c_subject</t>
   </si>
   <si>
-    <t>c_work_discipline</t>
-  </si>
-  <si>
     <t>c_location</t>
   </si>
   <si>
@@ -43,34 +62,169 @@
     <t>c_file</t>
   </si>
   <si>
+    <t>c_rfit_cost_implication</t>
+  </si>
+  <si>
+    <t>c_rfit_time_implication</t>
+  </si>
+  <si>
+    <t>c_requested_by</t>
+  </si>
+  <si>
+    <t>c_remarks</t>
+  </si>
+  <si>
+    <t>c_actioner</t>
+  </si>
+  <si>
+    <t>c_action</t>
+  </si>
+  <si>
+    <t>c_action_date</t>
+  </si>
+  <si>
+    <t>c_status</t>
+  </si>
+  <si>
     <t>c_issued_by</t>
   </si>
   <si>
     <t>c_date_issued</t>
   </si>
   <si>
+    <t>c_issue_designation</t>
+  </si>
+  <si>
+    <t>c_issuer_remark</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge</t>
+  </si>
+  <si>
+    <t>c_acknowledged_by</t>
+  </si>
+  <si>
+    <t>c_acknowledge_position</t>
+  </si>
+  <si>
+    <t>c_acknowledge_company</t>
+  </si>
+  <si>
+    <t>c_acknowledged_time</t>
+  </si>
+  <si>
+    <t>c_acknowledged_date</t>
+  </si>
+  <si>
     <t>c_response_desc</t>
   </si>
   <si>
     <t>c_re_applicable</t>
   </si>
   <si>
+    <t>c_re_applicable_remarks</t>
+  </si>
+  <si>
+    <t>c_response_file</t>
+  </si>
+  <si>
+    <t>c_cost_implication</t>
+  </si>
+  <si>
+    <t>c_time_extension</t>
+  </si>
+  <si>
     <t>c_reviewed_by</t>
   </si>
   <si>
-    <t>c_acknowledged_date</t>
-  </si>
-  <si>
-    <t>c_acknowledged_by</t>
-  </si>
-  <si>
-    <t>c_actioner</t>
-  </si>
-  <si>
-    <t>c_action</t>
-  </si>
-  <si>
-    <t>c_status</t>
+    <t>c_respond_designation</t>
+  </si>
+  <si>
+    <t>c_reviewer_organization</t>
+  </si>
+  <si>
+    <t>c_reviewed_date</t>
+  </si>
+  <si>
+    <t>c_rfi_acknowledge2</t>
+  </si>
+  <si>
+    <t>c_acknowledged_by2</t>
+  </si>
+  <si>
+    <t>c_acknowledge_position2</t>
+  </si>
+  <si>
+    <t>c_acknowledged_time2</t>
+  </si>
+  <si>
+    <t>c_acknowledged_date2</t>
+  </si>
+  <si>
+    <t>c_response_desc2</t>
+  </si>
+  <si>
+    <t>c_recommendation</t>
+  </si>
+  <si>
+    <t>c_response_remarks2</t>
+  </si>
+  <si>
+    <t>c_response_file2</t>
+  </si>
+  <si>
+    <t>c_reviewed_by2</t>
+  </si>
+  <si>
+    <t>c_respond_designation2</t>
+  </si>
+  <si>
+    <t>c_reviewer_organization2</t>
+  </si>
+  <si>
+    <t>c_reviewed_date2</t>
+  </si>
+  <si>
+    <t>c_response_desc3</t>
+  </si>
+  <si>
+    <t>c_response_file3</t>
+  </si>
+  <si>
+    <t>c_reviewed_by3</t>
+  </si>
+  <si>
+    <t>c_respond_designation3</t>
+  </si>
+  <si>
+    <t>c_reviewer_organization3</t>
+  </si>
+  <si>
+    <t>c_reviewed_date3</t>
+  </si>
+  <si>
+    <t>c_compile_dcr</t>
+  </si>
+  <si>
+    <t>c_compile_remarks</t>
+  </si>
+  <si>
+    <t>c_compile_file</t>
+  </si>
+  <si>
+    <t>c_compile_reviewed_by</t>
+  </si>
+  <si>
+    <t>c_compile_reviewer_organization</t>
+  </si>
+  <si>
+    <t>c_compile_reviewed_date</t>
+  </si>
+  <si>
+    <t>c_closed_remark</t>
+  </si>
+  <si>
+    <t>c_close_attachment</t>
   </si>
   <si>
     <t>RFIT No.</t>
@@ -79,12 +233,18 @@
     <t>Date</t>
   </si>
   <si>
+    <t>Work Discipline</t>
+  </si>
+  <si>
+    <t>Utility Provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Utility Provider Other</t>
+  </si>
+  <si>
     <t>RFIT Subject Title</t>
   </si>
   <si>
-    <t>Work Discipline</t>
-  </si>
-  <si>
     <t>Location/Chainage</t>
   </si>
   <si>
@@ -94,40 +254,178 @@
     <t>Attachment(s)</t>
   </si>
   <si>
+    <t>Cost Implication?</t>
+  </si>
+  <si>
+    <t>Time Implication?</t>
+  </si>
+  <si>
+    <t>Requested By</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Actioner</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Action Date</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>Issued By</t>
   </si>
   <si>
     <t>Issued Date</t>
   </si>
   <si>
+    <t>Issue Designation</t>
+  </si>
+  <si>
+    <t>Issue Remark</t>
+  </si>
+  <si>
+    <t>Acknowledge?</t>
+  </si>
+  <si>
+    <t>Acknowledged Name</t>
+  </si>
+  <si>
+    <t>Acknowledged Position</t>
+  </si>
+  <si>
+    <t>Acknowledged Company</t>
+  </si>
+  <si>
+    <t>Acknowledge Time</t>
+  </si>
+  <si>
+    <t>Acknowledge Date</t>
+  </si>
+  <si>
     <t>Response (RE)</t>
   </si>
   <si>
     <t>Applicable for Consultant RE to Review?</t>
   </si>
   <si>
+    <t>Response Remarks</t>
+  </si>
+  <si>
+    <t>Response Attachment(s)</t>
+  </si>
+  <si>
+    <t>Time Extension?</t>
+  </si>
+  <si>
     <t>Reviewed &amp; Approved By</t>
   </si>
   <si>
-    <t>Acknowledge Date</t>
-  </si>
-  <si>
-    <t>Acknowledge By</t>
-  </si>
-  <si>
-    <t>Actioner</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Status</t>
+    <t>Reviewed &amp; Approved Designation</t>
+  </si>
+  <si>
+    <t>Reviewed &amp; Approved Organization</t>
+  </si>
+  <si>
+    <t>Reviewed &amp; Approved Date</t>
+  </si>
+  <si>
+    <t>Acknowledge (PMC)</t>
+  </si>
+  <si>
+    <t>Acknowledge (PMC) By</t>
+  </si>
+  <si>
+    <t>Acknowledge (PMC) Position</t>
+  </si>
+  <si>
+    <t>Acknowledge (PMC) Time</t>
+  </si>
+  <si>
+    <t>Acknowledge (PMC) Date</t>
+  </si>
+  <si>
+    <t>Response (PMC)</t>
+  </si>
+  <si>
+    <t>Response (PMC) Recommendation</t>
+  </si>
+  <si>
+    <t>Response (PMC) Remarks</t>
+  </si>
+  <si>
+    <t>Response (PMC) attachment(s)</t>
+  </si>
+  <si>
+    <t>Reviewed &amp; Response (PMC) By</t>
+  </si>
+  <si>
+    <t>Reviewed &amp; Response (PMC) Designation</t>
+  </si>
+  <si>
+    <t>Reviewed &amp; Response (PMC) Organization</t>
+  </si>
+  <si>
+    <t>Reviewed &amp; Response (PMC) Date</t>
+  </si>
+  <si>
+    <t>Reviewed &amp; Response (SOR) Response</t>
+  </si>
+  <si>
+    <t>Reviewed &amp; Approved (SOR) Attachment(s)</t>
+  </si>
+  <si>
+    <t>Reviewed &amp; Response (SOR) By</t>
+  </si>
+  <si>
+    <t>Reviewed &amp; Response (SOR) Designation</t>
+  </si>
+  <si>
+    <t>Reviewed &amp; Response (SOR) Organization</t>
+  </si>
+  <si>
+    <t>Reviewed &amp; Response (SOR) Date</t>
+  </si>
+  <si>
+    <t>Design Change Request (DCR) ?</t>
+  </si>
+  <si>
+    <t>Design Change Request (DCR) Cost Implication?</t>
+  </si>
+  <si>
+    <t>Design Change Request (DCR) Time Extension?</t>
+  </si>
+  <si>
+    <t>Design Change Request (DCR) Remarks</t>
+  </si>
+  <si>
+    <t>Design Change Request (DCR) Attachment(s)</t>
+  </si>
+  <si>
+    <t>Compile &amp; Reviewed By</t>
+  </si>
+  <si>
+    <t>Compile &amp; Reviewed Organization</t>
+  </si>
+  <si>
+    <t>Compile &amp; Reviewed Date</t>
+  </si>
+  <si>
+    <t>Closed Remarks</t>
+  </si>
+  <si>
+    <t>Close Attachment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
@@ -1091,18 +1389,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:BN5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="7" max="7" width="22.3333333333333" customWidth="1"/>
-    <col min="9" max="11" width="15" customWidth="1"/>
-    <col min="12" max="13" width="21.6666666666667" customWidth="1"/>
-    <col min="14" max="16" width="21.8888888888889" customWidth="1"/>
-    <col min="17" max="17" width="6.44444444444444" customWidth="1"/>
+    <col min="3" max="3" width="16.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="16.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="22.7777777777778" customWidth="1"/>
+    <col min="6" max="6" width="16.2222222222222" customWidth="1"/>
+    <col min="9" max="9" width="22.3333333333333" customWidth="1"/>
+    <col min="10" max="13" width="11.6666666666667" customWidth="1"/>
+    <col min="14" max="15" width="21.8888888888889" customWidth="1"/>
+    <col min="16" max="16" width="14.5555555555556" customWidth="1"/>
+    <col min="17" max="17" width="8.44444444444444" customWidth="1"/>
+    <col min="18" max="18" width="11.6666666666667" customWidth="1"/>
+    <col min="19" max="25" width="15" customWidth="1"/>
+    <col min="26" max="26" width="21.1111111111111" customWidth="1"/>
+    <col min="27" max="27" width="15" customWidth="1"/>
+    <col min="28" max="28" width="16.2222222222222" customWidth="1"/>
+    <col min="29" max="29" width="15" customWidth="1"/>
+    <col min="30" max="65" width="21.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1112,11 +1420,11 @@
       <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:66">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1168,8 +1476,155 @@
       <c r="Q2" t="s">
         <v>1</v>
       </c>
+      <c r="R2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:66">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1221,8 +1676,155 @@
       <c r="Q3">
         <v>16</v>
       </c>
+      <c r="R3">
+        <v>17</v>
+      </c>
+      <c r="S3">
+        <v>18</v>
+      </c>
+      <c r="T3">
+        <v>19</v>
+      </c>
+      <c r="U3">
+        <v>20</v>
+      </c>
+      <c r="V3">
+        <v>21</v>
+      </c>
+      <c r="W3">
+        <v>22</v>
+      </c>
+      <c r="X3">
+        <v>23</v>
+      </c>
+      <c r="Y3">
+        <v>24</v>
+      </c>
+      <c r="Z3">
+        <v>25</v>
+      </c>
+      <c r="AA3">
+        <v>26</v>
+      </c>
+      <c r="AB3">
+        <v>27</v>
+      </c>
+      <c r="AC3">
+        <v>28</v>
+      </c>
+      <c r="AD3">
+        <v>29</v>
+      </c>
+      <c r="AE3">
+        <v>30</v>
+      </c>
+      <c r="AF3">
+        <v>31</v>
+      </c>
+      <c r="AG3">
+        <v>32</v>
+      </c>
+      <c r="AH3">
+        <v>33</v>
+      </c>
+      <c r="AI3">
+        <v>34</v>
+      </c>
+      <c r="AJ3">
+        <v>35</v>
+      </c>
+      <c r="AK3">
+        <v>36</v>
+      </c>
+      <c r="AL3">
+        <v>37</v>
+      </c>
+      <c r="AM3">
+        <v>38</v>
+      </c>
+      <c r="AN3">
+        <v>39</v>
+      </c>
+      <c r="AO3">
+        <v>40</v>
+      </c>
+      <c r="AP3">
+        <v>41</v>
+      </c>
+      <c r="AQ3">
+        <v>42</v>
+      </c>
+      <c r="AR3">
+        <v>43</v>
+      </c>
+      <c r="AS3">
+        <v>44</v>
+      </c>
+      <c r="AT3">
+        <v>45</v>
+      </c>
+      <c r="AU3">
+        <v>46</v>
+      </c>
+      <c r="AV3">
+        <v>47</v>
+      </c>
+      <c r="AW3">
+        <v>48</v>
+      </c>
+      <c r="AX3">
+        <v>49</v>
+      </c>
+      <c r="AY3">
+        <v>50</v>
+      </c>
+      <c r="AZ3">
+        <v>51</v>
+      </c>
+      <c r="BA3">
+        <v>52</v>
+      </c>
+      <c r="BB3">
+        <v>53</v>
+      </c>
+      <c r="BC3">
+        <v>54</v>
+      </c>
+      <c r="BD3">
+        <v>55</v>
+      </c>
+      <c r="BE3">
+        <v>56</v>
+      </c>
+      <c r="BF3">
+        <v>57</v>
+      </c>
+      <c r="BG3">
+        <v>58</v>
+      </c>
+      <c r="BH3">
+        <v>59</v>
+      </c>
+      <c r="BI3">
+        <v>60</v>
+      </c>
+      <c r="BJ3">
+        <v>61</v>
+      </c>
+      <c r="BK3">
+        <v>62</v>
+      </c>
+      <c r="BL3">
+        <v>63</v>
+      </c>
+      <c r="BM3">
+        <v>64</v>
+      </c>
+      <c r="BN3">
+        <v>65</v>
+      </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:66">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1274,58 +1876,352 @@
       <c r="Q4" t="s">
         <v>18</v>
       </c>
+      <c r="R4" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" t="s">
+        <v>20</v>
+      </c>
+      <c r="T4" t="s">
+        <v>21</v>
+      </c>
+      <c r="U4" t="s">
+        <v>22</v>
+      </c>
+      <c r="V4" t="s">
+        <v>23</v>
+      </c>
+      <c r="W4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>54</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>55</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>56</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>57</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>58</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>33</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>34</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>65</v>
+      </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:66">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="L5" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="M5" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="N5" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="O5" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="P5" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="Q5" t="s">
-        <v>35</v>
+        <v>82</v>
+      </c>
+      <c r="R5" t="s">
+        <v>83</v>
+      </c>
+      <c r="S5" t="s">
+        <v>84</v>
+      </c>
+      <c r="T5" t="s">
+        <v>85</v>
+      </c>
+      <c r="U5" t="s">
+        <v>86</v>
+      </c>
+      <c r="V5" t="s">
+        <v>87</v>
+      </c>
+      <c r="W5" t="s">
+        <v>88</v>
+      </c>
+      <c r="X5" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>101</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>105</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>106</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>107</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>114</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>116</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>117</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>120</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>121</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>122</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>123</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>124</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>125</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>126</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>127</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>129</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
